--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Донецк 130133080.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Донецк 130133080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A099048-F62D-41E3-AEC7-783339392EF9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864AA364-C697-42DD-ACEC-60DD090107CC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам.</t>
+  </si>
+  <si>
+    <t>ООО "НОВОЕ ВРЕМЯ" Мариуполь</t>
   </si>
 </sst>
 </file>
@@ -744,14 +747,6 @@
     <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -764,14 +759,22 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -780,47 +783,7 @@
     <cellStyle name="Обычный 13" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1280,14 +1243,14 @@
       <c r="D1" s="54">
         <v>130133080</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="58"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="64"/>
       <c r="K1" s="26">
         <v>130133079</v>
       </c>
@@ -1330,12 +1293,12 @@
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="G3" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="64"/>
       <c r="K3" s="26">
         <v>130133081</v>
       </c>
@@ -1373,6 +1336,12 @@
       <c r="G5" s="8"/>
       <c r="H5" s="21"/>
       <c r="I5" s="21"/>
+      <c r="K5" s="26">
+        <v>130439503</v>
+      </c>
+      <c r="L5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="37" t="s">
@@ -1465,7 +1434,7 @@
       <c r="J11" s="41"/>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="60">
+      <c r="A12" s="56">
         <v>5897</v>
       </c>
       <c r="B12" s="48" t="s">
@@ -1494,7 +1463,7 @@
       <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="60">
+      <c r="A13" s="56">
         <v>6149</v>
       </c>
       <c r="B13" s="48" t="s">
@@ -1523,7 +1492,7 @@
       <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="60">
+      <c r="A14" s="56">
         <v>6819</v>
       </c>
       <c r="B14" s="48" t="s">
@@ -1552,7 +1521,7 @@
       <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="60">
+      <c r="A15" s="56">
         <v>6202</v>
       </c>
       <c r="B15" s="48" t="s">
@@ -1581,7 +1550,7 @@
       <c r="J15" s="28"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="60">
+      <c r="A16" s="56">
         <v>6148</v>
       </c>
       <c r="B16" s="48" t="s">
@@ -1610,7 +1579,7 @@
       <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="60">
+      <c r="A17" s="56">
         <v>6209</v>
       </c>
       <c r="B17" s="48" t="s">
@@ -1639,7 +1608,7 @@
       <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="60">
+      <c r="A18" s="56">
         <v>6168</v>
       </c>
       <c r="B18" s="48" t="s">
@@ -1668,7 +1637,7 @@
       <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="60">
+      <c r="A19" s="56">
         <v>5579</v>
       </c>
       <c r="B19" s="48" t="s">
@@ -1697,10 +1666,10 @@
       <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="61">
+      <c r="A20" s="57">
         <v>5754</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="58" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="46" t="s">
@@ -1713,7 +1682,7 @@
       <c r="F20" s="22">
         <v>4.5</v>
       </c>
-      <c r="G20" s="63">
+      <c r="G20" s="59">
         <f>E20</f>
         <v>0</v>
       </c>
@@ -1726,7 +1695,7 @@
       <c r="J20" s="28"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="61">
+      <c r="A21" s="57">
         <v>5755</v>
       </c>
       <c r="B21" s="48" t="s">
@@ -1742,7 +1711,7 @@
       <c r="F21" s="22">
         <v>4.5</v>
       </c>
-      <c r="G21" s="63">
+      <c r="G21" s="59">
         <f>E21</f>
         <v>0</v>
       </c>
@@ -1756,20 +1725,20 @@
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="52"/>
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="66"/>
     </row>
     <row r="23" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="65">
+      <c r="A23" s="60">
         <v>7216</v>
       </c>
       <c r="B23" s="53" t="s">
@@ -1778,14 +1747,14 @@
       <c r="C23" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="66">
+      <c r="D23" s="61">
         <v>1002116437216</v>
       </c>
       <c r="E23" s="50"/>
       <c r="F23" s="22">
         <v>0.7</v>
       </c>
-      <c r="G23" s="63">
+      <c r="G23" s="59">
         <f>E23*F23</f>
         <v>0</v>
       </c>

--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Донецк 130133080.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Донецк 130133080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864AA364-C697-42DD-ACEC-60DD090107CC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CF6B32-3D67-422B-A7CA-87BD6E59BBAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -175,6 +175,27 @@
   <si>
     <t>ООО "НОВОЕ ВРЕМЯ" Мариуполь</t>
   </si>
+  <si>
+    <t>ОСТАНКИНСКИЕ пельм кор.0.5кг зам_NEW</t>
+  </si>
+  <si>
+    <t>С КАРТОФ.И ГРИБ.вареники пл.0.42кг зам.</t>
+  </si>
+  <si>
+    <t>ОСТАНКИНСКИЕ пельм пл. 0.7кг 10шт.зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм пл.0.42кг зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм пл.0.7кг зам.</t>
+  </si>
+  <si>
+    <t>МЯСНЫЕ ПРЕМИУМ пельм кор.0.4кг зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм 4кг зам.</t>
+  </si>
 </sst>
 </file>
 
@@ -302,7 +323,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,20 +371,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="lightHorizontal">
-        <fgColor indexed="42"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -548,30 +557,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="57"/>
-      </left>
-      <right style="double">
-        <color indexed="57"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -586,7 +571,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -729,17 +714,8 @@
     <xf numFmtId="2" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -750,20 +726,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -783,48 +750,7 @@
     <cellStyle name="Обычный 13" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1240,17 +1166,17 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="54">
+      <c r="D1" s="51">
         <v>130133080</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="64"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="58"/>
       <c r="K1" s="26">
         <v>130133079</v>
       </c>
@@ -1283,22 +1209,22 @@
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="55">
+      <c r="D3" s="52">
         <v>46209</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="55">
+      <c r="F3" s="52">
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="G3" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58"/>
       <c r="K3" s="26">
         <v>130133081</v>
       </c>
@@ -1434,7 +1360,8 @@
       <c r="J11" s="41"/>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="56">
+      <c r="A12" s="53" t="str">
+        <f>RIGHT(D12,4)</f>
         <v>5897</v>
       </c>
       <c r="B12" s="48" t="s">
@@ -1463,7 +1390,8 @@
       <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="56">
+      <c r="A13" s="53" t="str">
+        <f t="shared" ref="A13:A30" si="0">RIGHT(D13,4)</f>
         <v>6149</v>
       </c>
       <c r="B13" s="48" t="s">
@@ -1480,7 +1408,7 @@
         <v>0.3</v>
       </c>
       <c r="G13" s="22">
-        <f t="shared" ref="G13:G19" si="0">E13*F13</f>
+        <f t="shared" ref="G13:G19" si="1">E13*F13</f>
         <v>0</v>
       </c>
       <c r="H13" s="14">
@@ -1492,7 +1420,8 @@
       <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="56">
+      <c r="A14" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6819</v>
       </c>
       <c r="B14" s="48" t="s">
@@ -1509,7 +1438,7 @@
         <v>0.3</v>
       </c>
       <c r="G14" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
@@ -1521,7 +1450,8 @@
       <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56">
+      <c r="A15" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6202</v>
       </c>
       <c r="B15" s="48" t="s">
@@ -1538,7 +1468,7 @@
         <v>0.3</v>
       </c>
       <c r="G15" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H15" s="14">
@@ -1550,7 +1480,8 @@
       <c r="J15" s="28"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="56">
+      <c r="A16" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6148</v>
       </c>
       <c r="B16" s="48" t="s">
@@ -1567,7 +1498,7 @@
         <v>0.3</v>
       </c>
       <c r="G16" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H16" s="14">
@@ -1579,7 +1510,8 @@
       <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="56">
+      <c r="A17" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6209</v>
       </c>
       <c r="B17" s="48" t="s">
@@ -1596,7 +1528,7 @@
         <v>0.35</v>
       </c>
       <c r="G17" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H17" s="14">
@@ -1608,7 +1540,8 @@
       <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="56">
+      <c r="A18" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6168</v>
       </c>
       <c r="B18" s="48" t="s">
@@ -1625,7 +1558,7 @@
         <v>0.35</v>
       </c>
       <c r="G18" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H18" s="14">
@@ -1637,7 +1570,8 @@
       <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="56">
+      <c r="A19" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5579</v>
       </c>
       <c r="B19" s="48" t="s">
@@ -1654,7 +1588,7 @@
         <v>0.42</v>
       </c>
       <c r="G19" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H19" s="14">
@@ -1666,10 +1600,11 @@
       <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="57">
+      <c r="A20" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5754</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="54" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="46" t="s">
@@ -1682,7 +1617,7 @@
       <c r="F20" s="22">
         <v>4.5</v>
       </c>
-      <c r="G20" s="59">
+      <c r="G20" s="55">
         <f>E20</f>
         <v>0</v>
       </c>
@@ -1695,7 +1630,8 @@
       <c r="J20" s="28"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="57">
+      <c r="A21" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5755</v>
       </c>
       <c r="B21" s="48" t="s">
@@ -1711,7 +1647,7 @@
       <c r="F21" s="22">
         <v>4.5</v>
       </c>
-      <c r="G21" s="59">
+      <c r="G21" s="55">
         <f>E21</f>
         <v>0</v>
       </c>
@@ -1723,136 +1659,249 @@
       </c>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="52"/>
-      <c r="B22" s="66" t="s">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="50"/>
+      <c r="B22" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-    </row>
-    <row r="23" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="60">
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+    </row>
+    <row r="23" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>7216</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="54" t="s">
         <v>44</v>
       </c>
       <c r="C23" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="61">
+      <c r="D23" s="47">
         <v>1002116437216</v>
       </c>
-      <c r="E23" s="50"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="22">
         <v>0.7</v>
       </c>
-      <c r="G23" s="59">
+      <c r="G23" s="55">
         <f>E23*F23</f>
         <v>0</v>
       </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-    </row>
-    <row r="24" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="49"/>
-      <c r="B24" s="43" t="s">
+      <c r="I23" s="14"/>
+      <c r="J23" s="28"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>6824</v>
+      </c>
+      <c r="B24" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="47">
+        <v>1002112606824</v>
+      </c>
+      <c r="E24" s="23"/>
+      <c r="F24" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="55">
+        <f t="shared" ref="G24:G29" si="2">E24*F24</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="28"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7049</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="47">
+        <v>1002151787049</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" s="22">
+        <v>0.42</v>
+      </c>
+      <c r="G25" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="28"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7085</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="47">
+        <v>1002112607085</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="G26" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="28"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7212</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="47">
+        <v>1002112857212</v>
+      </c>
+      <c r="E27" s="23"/>
+      <c r="F27" s="22">
+        <v>0.42</v>
+      </c>
+      <c r="G27" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="28"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7214</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="47">
+        <v>1002112857214</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="G28" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="28"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7224</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="47">
+        <v>1002116517224</v>
+      </c>
+      <c r="E29" s="23"/>
+      <c r="F29" s="22">
+        <v>0.4</v>
+      </c>
+      <c r="G29" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7375</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="47">
+        <v>1002112857375</v>
+      </c>
+      <c r="E30" s="23"/>
+      <c r="F30" s="22">
+        <v>1</v>
+      </c>
+      <c r="G30" s="55">
+        <f>E30</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="28"/>
+    </row>
+    <row r="31" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="49"/>
+      <c r="B31" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="16">
-        <f>SUM(E10:E23)</f>
+      <c r="C31" s="15"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="16">
+        <f>SUM(E10:E30)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16">
-        <f>SUM(G12:G23)</f>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16">
+        <f>SUM(G10:G30)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="35"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="38"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="20"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="35"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="38"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="20"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="35"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="38"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="20"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="35"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="38"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="20"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="35"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="38"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="20"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="35"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="38"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="35"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="38"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="20"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B32" s="35"/>
       <c r="C32" s="17"/>
       <c r="D32" s="38"/>
@@ -16917,16 +16966,6 @@
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="B22:J22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="17" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
